--- a/data/public-data.xlsx
+++ b/data/public-data.xlsx
@@ -11,7 +11,7 @@
     <sheet name="第二十八屆高中菁英盃" sheetId="4" r:id="rId7"/>
     <sheet name="火雞肉飯盃" sheetId="5" r:id="rId8"/>
     <sheet name="火雞盃" sheetId="6" r:id="rId9"/>
-    <sheet name="火雞盃-1" sheetId="7" r:id="rId10"/>
+    <sheet name="吊嘎盃全國高中職辯論比賽" sheetId="7" r:id="rId10"/>
     <sheet name="輔仁盃" sheetId="8" r:id="rId11"/>
     <sheet name="風雩盃" sheetId="9" r:id="rId12"/>
     <sheet name="青雲盃" sheetId="10" r:id="rId13"/>
@@ -2933,7 +2933,7 @@
     <col min="4" max="5" width="8" style="1" customWidth="1"/>
     <col min="6" max="7" width="20" style="1" customWidth="1"/>
     <col min="8" max="9" width="11" style="1" customWidth="1"/>
-    <col min="10" max="10" width="23.9844" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24" style="1" customWidth="1"/>
     <col min="11" max="12" width="15" style="1" customWidth="1"/>
     <col min="13" max="13" width="20" style="1" customWidth="1"/>
     <col min="14" max="14" width="12" style="1" customWidth="1"/>
@@ -7117,10 +7117,10 @@
       <c r="K18" t="s" s="51">
         <v>49</v>
       </c>
-      <c r="L18" s="52"/>
-      <c r="M18" t="s" s="51">
+      <c r="L18" t="s" s="51">
         <v>117</v>
       </c>
+      <c r="M18" s="52"/>
       <c r="N18" t="s" s="51">
         <v>50</v>
       </c>
@@ -7144,10 +7144,10 @@
       <c r="K19" t="s" s="51">
         <v>51</v>
       </c>
-      <c r="L19" s="52"/>
-      <c r="M19" t="s" s="51">
+      <c r="L19" t="s" s="51">
         <v>45</v>
       </c>
+      <c r="M19" s="52"/>
       <c r="N19" t="s" s="51">
         <v>50</v>
       </c>
@@ -7171,10 +7171,10 @@
       <c r="K20" t="s" s="51">
         <v>52</v>
       </c>
-      <c r="L20" s="52"/>
-      <c r="M20" t="s" s="51">
+      <c r="L20" t="s" s="51">
         <v>123</v>
       </c>
+      <c r="M20" s="52"/>
       <c r="N20" t="s" s="51">
         <v>50</v>
       </c>
